--- a/report_2407.xlsx
+++ b/report_2407.xlsx
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>-0.06</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.68</v>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>4.78</v>
+        <v>6.37</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>4.78</v>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>16.25</v>
+        <v>14.94</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>16.25</v>
@@ -9028,13 +9028,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="97" t="inlineStr">
+      <c r="A25" s="78" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>24.17</v>
+        <v>60.63</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>24.17</v>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>24.17</v>
+        <v>60.63</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>24.17</v>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-0.02</v>
+        <v>1.48</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-0.02</v>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>4.41</v>
+        <v>3.94</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>4.41</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>47.02</v>
+        <v>58.95</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>47.02</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>54.79</v>
+        <v>59.54</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>54.79</v>
@@ -9772,9 +9772,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B32" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C32" s="94" t="inlineStr">
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>8.94</v>
+        <v>11.4</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>8.94</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>22.09</v>
+        <v>20.45</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>22.09</v>
@@ -10118,13 +10118,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="97" t="inlineStr">
+      <c r="A35" s="78" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>35.33</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>35.33</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>35.33</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>35.33</v>
@@ -13039,7 +13039,7 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RSI6:28.61&lt;=30;us500:RSI2:24.17&lt;=28;ixic:RSI2:35.33&lt;=36</t>
+          <t>今日买报：hk50:RSI6:28.61&lt;=30</t>
         </is>
       </c>
     </row>
